--- a/data_files/team_records_cleaned.xlsx
+++ b/data_files/team_records_cleaned.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -527,6 +532,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -558,6 +568,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -589,6 +604,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -620,6 +640,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -651,6 +676,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -682,6 +712,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -713,6 +748,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -744,6 +784,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,6 +820,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -806,6 +856,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -837,6 +892,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -868,6 +928,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -899,6 +964,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -930,6 +1000,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -961,6 +1036,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -994,6 +1074,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1027,6 +1112,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1058,6 +1148,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1089,6 +1184,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1120,6 +1220,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1151,6 +1256,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1182,6 +1292,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1213,6 +1328,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1244,6 +1364,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1275,6 +1400,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1306,6 +1436,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1337,6 +1472,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1368,6 +1508,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1399,6 +1544,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1429,6 +1579,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1442,7 +1597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1491,6 +1646,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1524,6 +1684,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1557,6 +1722,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1588,6 +1758,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1621,6 +1796,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1652,6 +1832,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1683,6 +1868,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1714,6 +1904,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1745,6 +1940,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1776,6 +1976,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1807,6 +2012,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1838,6 +2048,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1869,6 +2084,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1900,6 +2120,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1931,6 +2156,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1962,6 +2192,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1995,6 +2230,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2026,6 +2266,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2059,6 +2304,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2090,6 +2340,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2121,6 +2376,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2154,6 +2414,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2185,6 +2450,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2216,6 +2486,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2247,6 +2522,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2278,6 +2558,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2309,6 +2594,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2340,6 +2630,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2371,6 +2666,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2402,6 +2702,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2432,6 +2737,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2445,7 +2755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2494,6 +2804,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2527,6 +2842,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2560,6 +2880,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2593,6 +2918,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2624,6 +2954,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2655,6 +2990,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2686,6 +3026,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2717,6 +3062,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2748,6 +3098,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2779,6 +3134,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2810,6 +3170,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2841,6 +3206,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2872,6 +3242,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2903,6 +3278,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2934,6 +3314,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2965,6 +3350,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2998,6 +3388,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3031,6 +3426,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3064,6 +3464,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3095,6 +3500,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3126,6 +3536,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3157,6 +3572,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3188,6 +3608,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3219,6 +3644,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3250,6 +3680,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3281,6 +3716,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3312,6 +3752,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3343,6 +3788,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3374,6 +3824,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3405,6 +3860,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3435,6 +3895,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3448,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3497,6 +3962,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3530,6 +4000,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3563,6 +4038,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3594,6 +4074,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3627,6 +4112,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3658,6 +4148,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3689,6 +4184,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3720,6 +4220,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3751,6 +4256,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3782,6 +4292,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3813,6 +4328,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3844,6 +4364,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3875,6 +4400,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3906,6 +4436,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3937,6 +4472,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3968,6 +4508,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4001,6 +4546,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4034,6 +4584,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4065,6 +4620,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4098,6 +4658,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4129,6 +4694,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4160,6 +4730,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4191,6 +4766,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4222,6 +4802,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4253,6 +4838,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4284,6 +4874,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4315,6 +4910,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4346,6 +4946,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4377,6 +4982,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4408,6 +5018,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>NOH</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4438,6 +5053,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4451,7 +5071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4500,6 +5120,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4533,6 +5158,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4566,6 +5196,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4597,6 +5232,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4628,6 +5268,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4661,6 +5306,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4692,6 +5342,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4723,6 +5378,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4754,6 +5414,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4785,6 +5450,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4816,6 +5486,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4847,6 +5522,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4878,6 +5558,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NJN</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4909,6 +5594,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4940,6 +5630,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4971,6 +5666,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5004,6 +5704,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5037,6 +5742,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5070,6 +5780,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5101,6 +5816,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5132,6 +5852,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5163,6 +5888,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5194,6 +5924,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5225,6 +5960,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5256,6 +5996,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5287,6 +6032,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5318,6 +6068,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5349,6 +6104,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5380,6 +6140,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5411,6 +6176,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5441,6 +6211,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>NOH</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5454,7 +6229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5503,6 +6278,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5536,6 +6316,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5569,6 +6354,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5602,6 +6392,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5633,6 +6428,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5664,6 +6464,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5695,6 +6500,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5726,6 +6536,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5757,6 +6572,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5788,6 +6608,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5819,6 +6644,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5850,6 +6680,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5881,6 +6716,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NJN</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5912,6 +6752,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5943,6 +6788,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5974,6 +6824,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6007,6 +6862,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6040,6 +6900,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6071,6 +6936,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6104,6 +6974,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6135,6 +7010,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6166,6 +7046,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6197,6 +7082,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>NOH</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6228,6 +7118,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6259,6 +7154,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6290,6 +7190,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6321,6 +7226,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6352,6 +7262,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6383,6 +7298,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6414,6 +7334,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6444,6 +7369,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6457,7 +7387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6506,6 +7436,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6539,6 +7474,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6572,6 +7512,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6603,6 +7548,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6636,6 +7586,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6667,6 +7622,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6698,6 +7658,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6729,6 +7694,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6760,6 +7730,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6791,6 +7766,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6822,6 +7802,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6853,6 +7838,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6884,6 +7874,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6915,6 +7910,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6946,6 +7946,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6977,6 +7982,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NJN</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7010,6 +8020,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7043,6 +8058,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7074,6 +8094,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7107,6 +8132,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7140,6 +8170,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7171,6 +8206,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7202,6 +8242,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7233,6 +8278,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7264,6 +8314,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7295,6 +8350,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7326,6 +8386,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>NOH</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7357,6 +8422,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7388,6 +8458,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7419,6 +8494,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7449,6 +8529,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -7462,7 +8547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7511,6 +8596,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7544,6 +8634,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7577,6 +8672,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7610,6 +8710,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7641,6 +8746,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7672,6 +8782,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7703,6 +8818,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7734,6 +8854,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7765,6 +8890,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7796,6 +8926,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7827,6 +8962,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7858,6 +8998,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NJN</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7889,6 +9034,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7920,6 +9070,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7951,6 +9106,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7982,6 +9142,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8015,6 +9180,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8048,6 +9218,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8081,6 +9256,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8114,6 +9294,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8145,6 +9330,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8176,6 +9366,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8207,6 +9402,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>NOH</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8238,6 +9438,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8269,6 +9474,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8300,6 +9510,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8331,6 +9546,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8362,6 +9582,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -8393,6 +9618,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8424,6 +9654,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8454,6 +9689,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -8467,7 +9707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8516,6 +9756,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8549,6 +9794,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8582,6 +9832,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8615,6 +9870,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8646,6 +9906,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8677,6 +9942,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8708,6 +9978,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8739,6 +10014,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8770,6 +10050,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8801,6 +10086,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8832,6 +10122,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>NJN</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8863,6 +10158,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8894,6 +10194,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8925,6 +10230,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8956,6 +10266,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8987,6 +10302,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9020,6 +10340,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9053,6 +10378,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>NOH</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9086,6 +10416,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9117,6 +10452,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9148,6 +10488,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9181,6 +10526,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9212,6 +10562,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9243,6 +10598,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9274,6 +10634,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9305,6 +10670,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9336,6 +10706,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9367,6 +10742,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9398,6 +10778,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9429,6 +10814,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9459,6 +10849,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -9472,7 +10867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9521,6 +10916,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9554,6 +10954,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9585,6 +10990,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9616,6 +11026,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9649,6 +11064,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9682,6 +11102,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9713,6 +11138,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NJN</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9744,6 +11174,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9775,6 +11210,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9806,6 +11246,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9837,6 +11282,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9868,6 +11318,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9899,6 +11354,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9930,6 +11390,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9961,6 +11426,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9992,6 +11462,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10025,6 +11500,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10058,6 +11538,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10089,6 +11574,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10120,6 +11610,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10153,6 +11648,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10184,6 +11684,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -10215,6 +11720,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10246,6 +11756,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -10277,6 +11792,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -10308,6 +11828,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>NOH</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -10339,6 +11864,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -10370,6 +11900,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -10401,6 +11936,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -10432,6 +11972,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -10462,6 +12007,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -10475,7 +12025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10524,6 +12074,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10557,6 +12112,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10590,6 +12150,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10621,6 +12186,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10654,6 +12224,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NJN</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10685,6 +12260,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10716,6 +12296,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10747,6 +12332,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10778,6 +12368,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10809,6 +12404,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10840,6 +12440,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10871,6 +12476,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10902,6 +12512,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10933,6 +12548,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10964,6 +12584,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10995,6 +12620,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11028,6 +12658,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11059,6 +12694,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11092,6 +12732,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11123,6 +12768,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11154,6 +12804,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11185,6 +12840,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -11218,6 +12878,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11249,6 +12914,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11280,6 +12950,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -11311,6 +12986,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>NOH</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -11342,6 +13022,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -11373,6 +13058,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -11404,6 +13094,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -11435,6 +13130,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -11465,6 +13165,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -11478,7 +13183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11527,6 +13232,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11560,6 +13270,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11591,6 +13306,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11622,6 +13342,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11653,6 +13378,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11684,6 +13414,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11715,6 +13450,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11746,6 +13486,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11777,6 +13522,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11808,6 +13558,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11839,6 +13594,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11870,6 +13630,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11901,6 +13666,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11932,6 +13702,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11963,6 +13738,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11994,6 +13774,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12027,6 +13812,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12058,6 +13848,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12089,6 +13884,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -12120,6 +13920,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -12151,6 +13956,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12182,6 +13992,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12213,6 +14028,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -12244,6 +14064,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -12275,6 +14100,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -12306,6 +14136,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -12337,6 +14172,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -12368,6 +14208,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -12399,6 +14244,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -12430,6 +14280,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -12460,6 +14315,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -12473,7 +14333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12522,6 +14382,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12555,6 +14420,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12588,6 +14458,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12619,6 +14494,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12652,6 +14532,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12683,6 +14568,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12714,6 +14604,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12745,6 +14640,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12776,6 +14676,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>NJN</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12807,6 +14712,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12838,6 +14748,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12869,6 +14784,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12900,6 +14820,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12931,6 +14856,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12962,6 +14892,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12993,6 +14928,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13026,6 +14966,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13059,6 +15004,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13090,6 +15040,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -13123,6 +15078,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -13154,6 +15114,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -13185,6 +15150,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -13216,6 +15186,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13247,6 +15222,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13278,6 +15258,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13309,6 +15294,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13340,6 +15330,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -13371,6 +15366,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -13402,6 +15402,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -13433,6 +15438,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -13463,6 +15473,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>NOH</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -13476,7 +15491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13525,6 +15540,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13558,6 +15578,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13589,6 +15614,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13622,6 +15652,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>NJN</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13653,6 +15688,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13684,6 +15724,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>NOH</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13715,6 +15760,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13746,6 +15796,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13777,6 +15832,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13808,6 +15868,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13839,6 +15904,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13870,6 +15940,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13901,6 +15976,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13932,6 +16012,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13963,6 +16048,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13994,6 +16084,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14027,6 +16122,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14058,6 +16158,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14091,6 +16196,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14122,6 +16232,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -14153,6 +16268,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -14184,6 +16304,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -14215,6 +16340,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -14246,6 +16376,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -14277,6 +16412,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -14308,6 +16448,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -14339,6 +16484,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -14370,6 +16520,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -14401,6 +16556,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -14431,6 +16591,11 @@
       </c>
       <c r="I30" t="n">
         <v>14</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -14444,7 +16609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14493,6 +16658,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14526,6 +16696,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14557,6 +16732,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14588,6 +16768,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14619,6 +16804,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14650,6 +16840,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14681,6 +16876,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14712,6 +16912,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14743,6 +16948,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14774,6 +16984,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14805,6 +17020,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14836,6 +17056,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14867,6 +17092,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14898,6 +17128,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14929,6 +17164,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14960,6 +17200,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14993,6 +17238,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -15024,6 +17274,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -15055,6 +17310,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -15086,6 +17346,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -15117,6 +17382,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -15148,6 +17418,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -15179,6 +17454,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -15210,6 +17490,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -15241,6 +17526,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -15272,6 +17562,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15303,6 +17598,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -15334,6 +17634,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15365,6 +17670,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -15396,6 +17706,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -15426,6 +17741,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -15439,7 +17759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15488,6 +17808,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15521,6 +17846,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15552,6 +17882,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15583,6 +17918,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15614,6 +17954,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15645,6 +17990,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15676,6 +18026,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15707,6 +18062,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15738,6 +18098,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15769,6 +18134,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15800,6 +18170,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15831,6 +18206,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15862,6 +18242,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -15893,6 +18278,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15924,6 +18314,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15955,6 +18350,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15988,6 +18388,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16019,6 +18424,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -16050,6 +18460,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -16081,6 +18496,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -16112,6 +18532,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -16143,6 +18568,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -16174,6 +18604,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -16205,6 +18640,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -16236,6 +18676,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -16267,6 +18712,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -16298,6 +18748,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -16329,6 +18784,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -16360,6 +18820,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -16391,6 +18856,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -16421,6 +18891,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -16434,7 +18909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16483,6 +18958,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16516,6 +18996,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16547,6 +19032,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16578,6 +19068,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16609,6 +19104,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16640,6 +19140,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16671,6 +19176,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16702,6 +19212,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16733,6 +19248,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16764,6 +19284,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16795,6 +19320,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16826,6 +19356,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16857,6 +19392,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16888,6 +19428,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16919,6 +19464,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16950,6 +19500,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16983,6 +19538,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17014,6 +19574,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17045,6 +19610,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -17076,6 +19646,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -17107,6 +19682,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -17138,6 +19718,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -17169,6 +19754,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -17200,6 +19790,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -17231,6 +19826,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -17262,6 +19862,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -17293,6 +19898,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -17324,6 +19934,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -17355,6 +19970,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -17386,6 +20006,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -17416,6 +20041,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -17429,7 +20059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17478,6 +20108,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17511,6 +20146,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17542,6 +20182,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17573,6 +20218,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17604,6 +20254,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17635,6 +20290,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17666,6 +20326,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17697,6 +20362,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17728,6 +20398,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17759,6 +20434,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17790,6 +20470,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17821,6 +20506,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17852,6 +20542,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17883,6 +20578,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17914,6 +20614,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -17945,6 +20650,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17978,6 +20688,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -18009,6 +20724,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -18040,6 +20760,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -18071,6 +20796,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -18102,6 +20832,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -18133,6 +20868,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -18164,6 +20904,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -18195,6 +20940,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -18226,6 +20976,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -18257,6 +21012,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -18288,6 +21048,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -18319,6 +21084,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -18350,6 +21120,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -18381,6 +21156,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -18411,6 +21191,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -18424,7 +21209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18473,6 +21258,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18506,6 +21296,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18537,6 +21332,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18568,6 +21368,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18599,6 +21404,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18630,6 +21440,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18661,6 +21476,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18692,6 +21512,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18723,6 +21548,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18754,6 +21584,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -18785,6 +21620,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -18816,6 +21656,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -18847,6 +21692,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18878,6 +21728,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18909,6 +21764,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18940,6 +21800,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18973,6 +21838,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -19004,6 +21874,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -19035,6 +21910,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -19066,6 +21946,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -19097,6 +21982,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -19128,6 +22018,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -19159,6 +22054,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -19190,6 +22090,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -19221,6 +22126,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -19252,6 +22162,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -19283,6 +22198,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -19314,6 +22234,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -19345,6 +22270,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -19376,6 +22306,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -19406,6 +22341,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -19419,7 +22359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19468,6 +22408,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19501,6 +22446,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19532,6 +22482,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19563,6 +22518,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19594,6 +22554,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19625,6 +22590,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19656,6 +22626,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19687,6 +22662,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19718,6 +22698,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19749,6 +22734,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -19780,6 +22770,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -19811,6 +22806,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -19842,6 +22842,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -19873,6 +22878,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19904,6 +22914,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -19935,6 +22950,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -19968,6 +22988,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -19999,6 +23024,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -20030,6 +23060,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -20061,6 +23096,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -20092,6 +23132,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -20123,6 +23168,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -20154,6 +23204,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -20185,6 +23240,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -20216,6 +23276,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -20247,6 +23312,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -20278,6 +23348,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -20309,6 +23384,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -20340,6 +23420,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -20371,6 +23456,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -20401,6 +23491,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -20414,7 +23509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20463,6 +23558,11 @@
           <t>Conference Ranking</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20496,6 +23596,11 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20527,6 +23632,11 @@
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20558,6 +23668,11 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20589,6 +23704,11 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20620,6 +23740,11 @@
       <c r="I6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20651,6 +23776,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20682,6 +23812,11 @@
       <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20713,6 +23848,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20744,6 +23884,11 @@
       <c r="I10" t="n">
         <v>9</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20775,6 +23920,11 @@
       <c r="I11" t="n">
         <v>10</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20806,6 +23956,11 @@
       <c r="I12" t="n">
         <v>11</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -20837,6 +23992,11 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -20868,6 +24028,11 @@
       <c r="I14" t="n">
         <v>13</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -20899,6 +24064,11 @@
       <c r="I15" t="n">
         <v>14</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -20930,6 +24100,11 @@
       <c r="I16" t="n">
         <v>15</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -20963,6 +24138,11 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -20994,6 +24174,11 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -21025,6 +24210,11 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -21056,6 +24246,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -21087,6 +24282,11 @@
       <c r="I21" t="n">
         <v>5</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -21118,6 +24318,11 @@
       <c r="I22" t="n">
         <v>6</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -21149,6 +24354,11 @@
       <c r="I23" t="n">
         <v>7</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -21180,6 +24390,11 @@
       <c r="I24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -21211,6 +24426,11 @@
       <c r="I25" t="n">
         <v>9</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -21242,6 +24462,11 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -21273,6 +24498,11 @@
       <c r="I27" t="n">
         <v>11</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -21304,6 +24534,11 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -21335,6 +24570,11 @@
       <c r="I29" t="n">
         <v>13</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -21366,6 +24606,11 @@
       <c r="I30" t="n">
         <v>14</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -21396,6 +24641,11 @@
       </c>
       <c r="I31" t="n">
         <v>15</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
       </c>
     </row>
   </sheetData>
